--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -194,22 +194,22 @@
     <x:t>Sabc</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server closing connection</x:t>
+  </x:si>
+  <x:si>
     <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server closing connection</x:t>
   </x:si>
   <x:si>
     <x:t>Client closing connection</x:t>
@@ -256,12 +256,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1104,10 +1104,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62929</x:v>
+        <x:v>51766</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>48</x:v>
@@ -1160,10 +1160,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62929</x:v>
+        <x:v>51766</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,10 +1216,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62929</x:v>
+        <x:v>51766</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>48</x:v>
@@ -1272,10 +1272,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62929</x:v>
+        <x:v>51766</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>48</x:v>
@@ -1319,22 +1319,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>62929</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>51766</x:v>
+      </x:c>
+      <x:c r="R6" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1369,28 +1369,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R7" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1431,22 +1431,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4004</x:v>
+        <x:v>51766</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>62929</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="R8" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1466,43 +1466,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
+      <x:c r="M9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="0">
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="Q9" s="0">
+        <x:v>51766</x:v>
+      </x:c>
+      <x:c r="R9" s="4" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>62929</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1552,10 +1552,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>62929</x:v>
+        <x:v>51766</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1578,11 +1578,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1593,7 +1593,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>64</x:v>
@@ -1608,13 +1608,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>62929</x:v>
+        <x:v>51766</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1649,28 +1649,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1720,10 +1720,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>62933</x:v>
+        <x:v>51777</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>48</x:v>
@@ -1776,10 +1776,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>62933</x:v>
+        <x:v>51777</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,10 +1832,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>62933</x:v>
+        <x:v>51777</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>48</x:v>
@@ -1888,10 +1888,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>62933</x:v>
+        <x:v>51777</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>48</x:v>
@@ -1944,13 +1944,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>62933</x:v>
+        <x:v>51777</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="R17" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="R17" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1985,28 +1985,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R18" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2056,13 +2056,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>62933</x:v>
-      </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>51777</x:v>
+      </x:c>
+      <x:c r="R19" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2082,43 +2082,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G20" s="0" t="s">
+      <x:c r="H20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
+      <x:c r="M20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P20" s="0">
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="Q20" s="0">
+        <x:v>51777</x:v>
+      </x:c>
+      <x:c r="R20" s="4" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="M20" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P20" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="Q20" s="0">
-        <x:v>62933</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2168,10 +2168,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>62933</x:v>
+        <x:v>51777</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2194,11 +2194,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -2209,7 +2209,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>64</x:v>
@@ -2224,13 +2224,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>62933</x:v>
+        <x:v>51777</x:v>
       </x:c>
       <x:c r="Q22" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="R22" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2265,28 +2265,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R23" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -194,6 +194,9 @@
     <x:t>Sabc</x:t>
   </x:si>
   <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
@@ -207,9 +210,6 @@
   </x:si>
   <x:si>
     <x:t>Server closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
     <x:t>Client closing connection</x:t>
@@ -256,12 +256,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1104,10 +1104,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>51766</x:v>
+        <x:v>55502</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>48</x:v>
@@ -1160,10 +1160,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>51766</x:v>
+        <x:v>55502</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,10 +1216,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>51766</x:v>
+        <x:v>55502</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>48</x:v>
@@ -1272,10 +1272,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>51766</x:v>
+        <x:v>55502</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>48</x:v>
@@ -1319,22 +1319,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4005</x:v>
+        <x:v>55502</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>51766</x:v>
-      </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1369,7 +1369,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1389,8 +1389,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R7" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1431,22 +1431,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>51766</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4005</x:v>
-      </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>55502</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1466,25 +1466,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>47</x:v>
@@ -1496,13 +1496,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>51766</x:v>
-      </x:c>
-      <x:c r="R9" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>55502</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1552,10 +1552,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>51766</x:v>
+        <x:v>55502</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1578,22 +1578,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>64</x:v>
@@ -1608,13 +1608,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>51766</x:v>
+        <x:v>55502</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4005</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1649,7 +1649,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1669,8 +1669,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R12" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1720,10 +1720,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>51777</x:v>
+        <x:v>55505</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>48</x:v>
@@ -1776,10 +1776,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>51777</x:v>
+        <x:v>55505</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,10 +1832,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>51777</x:v>
+        <x:v>55505</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>48</x:v>
@@ -1888,10 +1888,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>51777</x:v>
+        <x:v>55505</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>48</x:v>
@@ -1944,13 +1944,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>51777</x:v>
+        <x:v>55505</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>4005</x:v>
-      </x:c>
-      <x:c r="R17" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1985,7 +1985,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
         <x:v>17</x:v>
@@ -2005,8 +2005,8 @@
       <x:c r="Q18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R18" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R18" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2056,13 +2056,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>51777</x:v>
-      </x:c>
-      <x:c r="R19" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>55505</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2082,25 +2082,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
         <x:v>47</x:v>
@@ -2112,13 +2112,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>51777</x:v>
-      </x:c>
-      <x:c r="R20" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>55505</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2168,10 +2168,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>51777</x:v>
+        <x:v>55505</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2194,22 +2194,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K22" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K22" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>64</x:v>
@@ -2224,13 +2224,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>51777</x:v>
+        <x:v>55505</x:v>
       </x:c>
       <x:c r="Q22" s="0">
-        <x:v>4005</x:v>
-      </x:c>
-      <x:c r="R22" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2265,7 +2265,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
         <x:v>17</x:v>
@@ -2285,8 +2285,8 @@
       <x:c r="Q23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R23" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,10 +1104,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>48</x:v>
@@ -1160,10 +1160,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,10 +1216,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>48</x:v>
@@ -1272,10 +1272,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>48</x:v>
@@ -1328,10 +1328,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>58</x:v>
@@ -1440,10 +1440,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1496,10 +1496,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1552,10 +1552,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,10 +1608,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55502</x:v>
+        <x:v>61867</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>58</x:v>
@@ -1720,10 +1720,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>48</x:v>
@@ -1776,10 +1776,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,10 +1832,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>48</x:v>
@@ -1888,10 +1888,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>48</x:v>
@@ -1944,10 +1944,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
         <x:v>58</x:v>
@@ -2056,10 +2056,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2112,10 +2112,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2168,10 +2168,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,10 +2224,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>55505</x:v>
+        <x:v>61873</x:v>
       </x:c>
       <x:c r="Q22" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
         <x:v>58</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,10 +1104,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>48</x:v>
@@ -1160,10 +1160,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,10 +1216,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>48</x:v>
@@ -1272,10 +1272,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>48</x:v>
@@ -1328,10 +1328,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>58</x:v>
@@ -1440,10 +1440,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1496,10 +1496,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1552,10 +1552,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,10 +1608,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>61867</x:v>
+        <x:v>59464</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>58</x:v>
@@ -1720,10 +1720,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>48</x:v>
@@ -1776,10 +1776,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,10 +1832,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>48</x:v>
@@ -1888,10 +1888,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>48</x:v>
@@ -1944,10 +1944,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
         <x:v>58</x:v>
@@ -2056,10 +2056,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2112,10 +2112,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2168,10 +2168,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,10 +2224,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>61873</x:v>
+        <x:v>59468</x:v>
       </x:c>
       <x:c r="Q22" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
         <x:v>58</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -194,22 +194,22 @@
     <x:t>Sabc</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server closing connection</x:t>
+  </x:si>
+  <x:si>
     <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server closing connection</x:t>
   </x:si>
   <x:si>
     <x:t>Client closing connection</x:t>
@@ -256,12 +256,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>59464</x:v>
+        <x:v>51946</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>59464</x:v>
+        <x:v>51946</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>59464</x:v>
+        <x:v>51946</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>59464</x:v>
+        <x:v>51946</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1319,22 +1319,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>59464</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>51946</x:v>
+      </x:c>
+      <x:c r="R6" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1369,28 +1369,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R7" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1431,22 +1431,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
+        <x:v>51946</x:v>
+      </x:c>
+      <x:c r="Q8" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q8" s="0">
-        <x:v>59464</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="R8" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1466,25 +1466,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>47</x:v>
@@ -1499,10 +1499,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>59464</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>51946</x:v>
+      </x:c>
+      <x:c r="R9" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>59464</x:v>
+        <x:v>51946</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1578,11 +1578,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1593,7 +1593,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>64</x:v>
@@ -1608,13 +1608,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>59464</x:v>
+        <x:v>51946</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="R11" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1649,28 +1649,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>59468</x:v>
+        <x:v>51951</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>59468</x:v>
+        <x:v>51951</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>59468</x:v>
+        <x:v>51951</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>59468</x:v>
+        <x:v>51951</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,13 +1944,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>59468</x:v>
+        <x:v>51951</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="R17" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="R17" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1985,28 +1985,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R18" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2059,10 +2059,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>59468</x:v>
-      </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>51951</x:v>
+      </x:c>
+      <x:c r="R19" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2082,25 +2082,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G20" s="0" t="s">
+      <x:c r="H20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
         <x:v>47</x:v>
@@ -2115,10 +2115,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>59468</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>51951</x:v>
+      </x:c>
+      <x:c r="R20" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>59468</x:v>
+        <x:v>51951</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2194,11 +2194,11 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -2209,7 +2209,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>64</x:v>
@@ -2224,13 +2224,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>59468</x:v>
+        <x:v>51951</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="R22" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2265,28 +2265,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R23" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -194,6 +194,9 @@
     <x:t>Sabc</x:t>
   </x:si>
   <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
@@ -207,9 +210,6 @@
   </x:si>
   <x:si>
     <x:t>Server closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
     <x:t>Client closing connection</x:t>
@@ -256,12 +256,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>51946</x:v>
+        <x:v>62630</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>51946</x:v>
+        <x:v>62630</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>51946</x:v>
+        <x:v>62630</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>51946</x:v>
+        <x:v>62630</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1319,22 +1319,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
+        <x:v>62630</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q6" s="0">
-        <x:v>51946</x:v>
-      </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>48</x:v>
+      <x:c r="R6" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1369,7 +1369,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1389,8 +1389,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R7" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1431,22 +1431,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>51946</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>62630</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1466,25 +1466,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>47</x:v>
@@ -1499,10 +1499,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>51946</x:v>
-      </x:c>
-      <x:c r="R9" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>62630</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>51946</x:v>
+        <x:v>62630</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1578,22 +1578,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>64</x:v>
@@ -1608,13 +1608,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>51946</x:v>
+        <x:v>62630</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="R11" s="4" t="s">
-        <x:v>63</x:v>
+      <x:c r="R11" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1649,7 +1649,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1669,8 +1669,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R12" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>51951</x:v>
+        <x:v>62633</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>51951</x:v>
+        <x:v>62633</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>51951</x:v>
+        <x:v>62633</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>51951</x:v>
+        <x:v>62633</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,13 +1944,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>51951</x:v>
+        <x:v>62633</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="R17" s="4" t="s">
-        <x:v>63</x:v>
+      <x:c r="R17" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1985,7 +1985,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
         <x:v>17</x:v>
@@ -2005,8 +2005,8 @@
       <x:c r="Q18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R18" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R18" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2059,10 +2059,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>51951</x:v>
-      </x:c>
-      <x:c r="R19" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>62633</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2082,25 +2082,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
         <x:v>47</x:v>
@@ -2115,10 +2115,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>51951</x:v>
-      </x:c>
-      <x:c r="R20" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>62633</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>51951</x:v>
+        <x:v>62633</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2194,22 +2194,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K22" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K22" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>64</x:v>
@@ -2224,13 +2224,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>51951</x:v>
+        <x:v>62633</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="R22" s="4" t="s">
-        <x:v>63</x:v>
+      <x:c r="R22" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2265,7 +2265,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
         <x:v>17</x:v>
@@ -2285,8 +2285,8 @@
       <x:c r="Q23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>59</x:v>
+      <x:c r="R23" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>62630</x:v>
+        <x:v>65227</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>62633</x:v>
+        <x:v>65230</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>65227</x:v>
+        <x:v>49951</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>65230</x:v>
+        <x:v>49954</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>49951</x:v>
+        <x:v>49191</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>49954</x:v>
+        <x:v>49194</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>49191</x:v>
+        <x:v>54254</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>49194</x:v>
+        <x:v>54257</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>54254</x:v>
+        <x:v>56551</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>54257</x:v>
+        <x:v>56556</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>56551</x:v>
+        <x:v>56300</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>56556</x:v>
+        <x:v>56304</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
